--- a/liste_eleves.xlsx
+++ b/liste_eleves.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t xml:space="preserve">Prénom NOM DE FAMILLE</t>
   </si>
@@ -29,9 +29,6 @@
   </si>
   <si>
     <t xml:space="preserve">Ornella ANTONY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-2026</t>
   </si>
   <si>
     <t xml:space="preserve">Niel ARMENGAUD</t>
@@ -159,11 +156,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -294,6 +291,7 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -308,140 +306,137 @@
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="0" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>3</v>
+      <c r="B3" s="2" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>3</v>
+      <c r="B12" s="2" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>3</v>
+        <v>14</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
+        <v>15</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="1"/>
+      <c r="A16" s="0"/>
+      <c r="B16" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="2"/>
+      <c r="A17" s="0"/>
+      <c r="B17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="2"/>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="1"/>
+      <c r="A18" s="0"/>
+      <c r="B18" s="0"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="2"/>
+      <c r="B20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="2"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="1"/>
+      <c r="B21" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="2"/>
+      <c r="B23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="2"/>
+      <c r="B24" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/liste_eleves.xlsx
+++ b/liste_eleves.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
   <si>
     <t xml:space="preserve">Prénom NOM DE FAMILLE</t>
   </si>
@@ -28,6 +28,318 @@
     <t xml:space="preserve">PROMOTION</t>
   </si>
   <si>
+    <t xml:space="preserve">Lucile CROSETTI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bastien DIDIER </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallulah FRAPPIER </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amandine HENAFF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quentin LALOUX </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clara LANTHIEZ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralie RETUREAU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riwad SALIM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valentin SOCHA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amélie SOUTSAMRANE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ariane ALCARAZ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julie BASSINOT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mustapha BENSALEM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Céline BOUVIER </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marjorie COLIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucie DORET </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Florian FRIER </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capucine GOUGELET </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lila LE FLOCH MEUNIER </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vincent POULET </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amélie ROGER </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inès ROUSSET </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathan AGRANAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charlène BRUN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicolas CHRISTMANN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice HERBRETEAU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bernadette KALAJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solène LOMBARD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sylvie NGUYEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grégoire ORMIÈRES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marion ROBIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clara SCHOENLAUB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Théo ROCQUANCOURT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice SANZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Léo BINDNER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alexiane CAPITAINE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">François DESOLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nais HOANG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathilde KAPPLER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jean-Baptiste KRAUSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Léo LAFFARGUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minh LÊ BOUTIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chloé MICHEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Léontine PIGOT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emma PUSTIENNE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marin SCART</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eva BARENTON </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Léane BEAUQUIS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pierre BOURDON </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabian CHAPPÉ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faustine DURAND-BUFFE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alix GAVALDA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice GIOIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marin POUSSET </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kélit RAYNAUD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Léa REVIRON </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emilie SALFATI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hector WILMOT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axel ANASTACIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quentin BENELFOUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mattéo CALIFANO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarisse HELIE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kamil IZARET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amelle RETIEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Léa TAING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Candice TIZIEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margaux VERGNAUD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ekaterina ZHITKOVSKAYA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antoine ASSANVO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Louane AVRANCHE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marilya BERTIDE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manon BOUCHER </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julie BREVET </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nelson DESAYO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annaëlle MATHIEU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quentin NOLOT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nasryne OUABI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emilia PESTY </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glenn ANDRO-UEDA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romain BLONDEL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romain BOURILLON </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maïwenn BROCHEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clémence BRUN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clémence CELERIER </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kim COUDEVILLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camille FAUXBATON </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eliès JURQUET </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leia MIR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Florian MONTUS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathilde SASSIER </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rémi AVIGNON </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titouan BESSENAY </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titouan BOIREAU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Philippe CHEVALIER </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basil NOORDANUS-CALMELS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eloïse GONIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zoé POUVREAU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lynn SIMAMORA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andréa TERROSO BOUCHARD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cléo TETART </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathieu TREHIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rachel TRUCHOT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arthur WARDENSKI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flore WODEY </t>
+  </si>
+  <si>
     <t xml:space="preserve">Ornella ANTONY</t>
   </si>
   <si>
@@ -68,6 +380,48 @@
   </si>
   <si>
     <t xml:space="preserve">Lucie ROBIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tess ANDERSON </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eve ARFI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kélio BOUTEFNOUCHET </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingrid CAZENAVE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emna CHAABANE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valentine DUPUY </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olivier FALAH </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rili KAJIYAMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elio MAHIEUX </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iwann REFFAIT-OUSSAADI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vic SADOT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serena TALEB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maureen VILLEMAGNE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Théo VIRGAUX </t>
   </si>
 </sst>
 </file>
@@ -77,7 +431,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -103,6 +457,11 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -147,7 +506,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -156,11 +515,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -287,7 +658,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:F143"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44.1"/>
@@ -303,140 +674,1096 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="0" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0"/>
+      <c r="B12" s="0"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B76" s="1" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B87" s="1" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B100" s="1" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B113" s="5" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B115" s="1" t="n">
         <v>2026</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="n">
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B116" s="4" t="n">
         <v>2026</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2" t="n">
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B117" s="4" t="n">
         <v>2026</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2" t="n">
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B118" s="4" t="n">
         <v>2026</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="n">
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B119" s="4" t="n">
         <v>2026</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="2" t="n">
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B120" s="4" t="n">
         <v>2026</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="2" t="n">
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B121" s="4" t="n">
         <v>2026</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="2" t="n">
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B122" s="4" t="n">
         <v>2026</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="2" t="n">
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B123" s="4" t="n">
         <v>2026</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="2" t="n">
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B124" s="4" t="n">
         <v>2026</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="2" t="n">
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B125" s="4" t="n">
         <v>2026</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="2" t="n">
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B126" s="4" t="n">
         <v>2026</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="2" t="n">
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B127" s="4" t="n">
         <v>2026</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="2" t="n">
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B128" s="4" t="n">
         <v>2026</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0"/>
-      <c r="B16" s="0"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0"/>
-      <c r="B17" s="0"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0"/>
-      <c r="B18" s="0"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="3"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="3"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="3"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="3"/>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="0"/>
+      <c r="B129" s="0"/>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B130" s="0" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B131" s="5" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B132" s="5" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B133" s="5" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B134" s="5" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B135" s="5" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B136" s="5" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B137" s="5" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B138" s="5" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B139" s="5" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B140" s="5" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B141" s="5" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B142" s="5" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B143" s="5" t="n">
+        <v>2027</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/liste_eleves.xlsx
+++ b/liste_eleves.xlsx
@@ -154,7 +154,7 @@
     <t xml:space="preserve">Albane HEITZ</t>
   </si>
   <si>
-    <t xml:space="preserve">@art.albane</t>
+    <t xml:space="preserve">@albane.htz</t>
   </si>
   <si>
     <t xml:space="preserve">Ulysse MIGEAT</t>
@@ -1114,11 +1114,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0"/>
-      <c r="B16" s="0"/>
-      <c r="C16" s="0"/>
-    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>31</v>
@@ -1276,11 +1272,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0"/>
-      <c r="B31" s="0"/>
-      <c r="C31" s="0"/>
-    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
         <v>59</v>
@@ -1438,11 +1430,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0"/>
-      <c r="B46" s="0"/>
-      <c r="C46" s="0"/>
-    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
         <v>87</v>
@@ -1578,11 +1566,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0"/>
-      <c r="B59" s="0"/>
-      <c r="C59" s="0"/>
-    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
         <v>111</v>
@@ -1694,11 +1678,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0"/>
-      <c r="B70" s="0"/>
-      <c r="C70" s="0"/>
-    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
         <v>130</v>
@@ -1796,11 +1776,7 @@
       </c>
       <c r="C80" s="5"/>
     </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0"/>
-      <c r="B81" s="0"/>
-      <c r="C81" s="0"/>
-    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="4" t="s">
         <v>142</v>
@@ -1926,11 +1902,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0"/>
-      <c r="B94" s="0"/>
-      <c r="C94" s="0"/>
-    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
         <v>161</v>
@@ -2052,11 +2024,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="0"/>
-      <c r="B107" s="0"/>
-      <c r="C107" s="0"/>
-    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
         <v>178</v>
@@ -2172,11 +2140,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="0"/>
-      <c r="B120" s="0"/>
-      <c r="C120" s="0"/>
-    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
         <v>192</v>
@@ -2290,11 +2254,7 @@
       </c>
       <c r="C132" s="5"/>
     </row>
-    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="0"/>
-      <c r="B133" s="0"/>
-      <c r="C133" s="0"/>
-    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2" t="s">
         <v>205</v>
@@ -2394,9 +2354,6 @@
       <c r="C143" s="5"/>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A144" s="0"/>
-      <c r="B144" s="0"/>
-      <c r="C144" s="0"/>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
       <c r="F144" s="1"/>
